--- a/WPF/DevExpress.HybridApp.Wpf/VB/DevExpress.HybridApp.Wpf/Resources/Analysis/CustomerAnalysis.xlsx
+++ b/WPF/DevExpress.HybridApp.Wpf/VB/DevExpress.HybridApp.Wpf/Resources/Analysis/CustomerAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VCS\2020.1\Demos.RealLife\DevExpress.OutlookInspiredApp\DevExpress.OutlookInspiredApp.Win\Resources\Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\2025.2\Demos.RealLife\DevExpress.OutlookInspiredApp\DevExpress.OutlookInspiredApp.Win\Resources\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312B2E73-60A6-48FC-91D9-DF56D610D606}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1407B310-4294-41F2-815D-D9746F47C96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22560" yWindow="-8740" windowWidth="31000" windowHeight="17510" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Report" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Sales Report'!$A$2:$M$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Sales Data'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sales Report'!$14:$14</definedName>
+    <definedName name="ReportYear">YEAR(TODAY())-1</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,6 +35,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -103,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -663,34 +686,34 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -699,7 +722,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -758,17 +781,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -778,71 +801,71 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -885,9 +908,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:colOff>2009140</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>400050</xdr:rowOff>
+      <xdr:rowOff>408940</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1273,49 +1296,49 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:L35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" customWidth="1"/>
-    <col min="9" max="9" width="3.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
-    <col min="13" max="13" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.6640625" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" customWidth="1"/>
+    <col min="7" max="7" width="3.6640625" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="3.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
+    <col min="11" max="11" width="3.6640625" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
+    <col min="13" max="13" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:12" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" ht="17.25" customHeight="1"/>
+    <row r="3" spans="2:12" ht="43.5" customHeight="1" thickBot="1">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="51" t="str">
-        <f ca="1">CONCATENATE("SALES ANALYSIS ", YEAR(TODAY())-1)</f>
-        <v>SALES ANALYSIS 2019</v>
-      </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-    </row>
-    <row r="4" spans="2:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="50" t="str" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">CONCATENATE("SALES ANALYSIS ", ReportYear)</f>
+        <v>SALES ANALYSIS 2025</v>
+      </c>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+    </row>
+    <row r="4" spans="2:12" ht="29.25" customHeight="1">
       <c r="B4" s="46" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="29.25" hidden="1" customHeight="1">
       <c r="B5" s="20"/>
     </row>
-    <row r="6" spans="2:12" s="1" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" s="1" customFormat="1" ht="20.399999999999999" customHeight="1">
       <c r="B6" s="44">
         <f>'Sales Data'!D6</f>
         <v>0</v>
@@ -1332,14 +1355,14 @@
         <f>'Sales Data'!G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="52">
+      <c r="J6" s="51">
         <f>'Sales Data'!H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="53"/>
-      <c r="L6" s="54"/>
-    </row>
-    <row r="7" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="52"/>
+      <c r="L6" s="53"/>
+    </row>
+    <row r="7" spans="2:12" ht="24" customHeight="1">
       <c r="B7" s="29">
         <f>SUM('Sales Data'!D31:D42)</f>
         <v>0</v>
@@ -1356,24 +1379,24 @@
         <f>SUM('Sales Data'!G31:G42)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="55">
+      <c r="J7" s="54">
         <f>SUM('Sales Data'!H31:H42)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="56"/>
-      <c r="L7" s="57"/>
-    </row>
-    <row r="8" spans="2:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+    </row>
+    <row r="8" spans="2:12" ht="37.5" customHeight="1">
       <c r="B8" s="21"/>
       <c r="D8" s="23"/>
       <c r="F8" s="23"/>
       <c r="H8" s="23"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="68"/>
-    </row>
-    <row r="9" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:12" s="1" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="65"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="67"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.899999999999999" customHeight="1"/>
+    <row r="10" spans="2:12" s="1" customFormat="1" ht="20.399999999999999" customHeight="1">
       <c r="B10" s="30">
         <f>'Sales Data'!I6</f>
         <v>0</v>
@@ -1390,14 +1413,14 @@
         <f>'Sales Data'!L6</f>
         <v>0</v>
       </c>
-      <c r="J10" s="60">
+      <c r="J10" s="59">
         <f>'Sales Data'!M6</f>
         <v>0</v>
       </c>
-      <c r="K10" s="61"/>
-      <c r="L10" s="62"/>
-    </row>
-    <row r="11" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="60"/>
+      <c r="L10" s="61"/>
+    </row>
+    <row r="11" spans="2:12" ht="24" customHeight="1">
       <c r="B11" s="29">
         <f>SUM('Sales Data'!I34:I45)</f>
         <v>0</v>
@@ -1414,62 +1437,62 @@
         <f>SUM('Sales Data'!L34:L45)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="63">
+      <c r="J11" s="62">
         <f>SUM('Sales Data'!M34:M45)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="64"/>
-      <c r="L11" s="65"/>
-    </row>
-    <row r="12" spans="2:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="63"/>
+      <c r="L11" s="64"/>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" customHeight="1">
       <c r="B12" s="21"/>
       <c r="D12" s="21"/>
       <c r="F12" s="23"/>
       <c r="H12" s="23"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="68"/>
-    </row>
-    <row r="13" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="65"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="67"/>
+    </row>
+    <row r="13" spans="2:12" ht="18.899999999999999" customHeight="1"/>
+    <row r="14" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B14" s="31"/>
       <c r="C14" s="32"/>
-      <c r="D14" s="58" t="str">
-        <f ca="1">CONCATENATE("FY ", YEAR(TODAY())-3)</f>
-        <v>FY 2017</v>
-      </c>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58" t="str">
-        <f ca="1">CONCATENATE("FY ", YEAR(TODAY())-2)</f>
-        <v>FY 2018</v>
-      </c>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58" t="str">
-        <f ca="1">CONCATENATE("FY ", YEAR(TODAY())-1)</f>
-        <v>FY 2019</v>
-      </c>
-      <c r="I14" s="58"/>
+      <c r="D14" s="57" t="str" cm="1">
+        <f t="array" aca="1" ref="D14" ca="1">CONCATENATE("FY ", ReportYear-2)</f>
+        <v>FY 2023</v>
+      </c>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57" t="str" cm="1">
+        <f t="array" aca="1" ref="F14" ca="1">CONCATENATE("FY ", ReportYear-1)</f>
+        <v>FY 2024</v>
+      </c>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57" t="str" cm="1">
+        <f t="array" aca="1" ref="H14" ca="1">CONCATENATE("FY ", ReportYear)</f>
+        <v>FY 2025</v>
+      </c>
+      <c r="I14" s="57"/>
       <c r="J14" s="32"/>
-      <c r="K14" s="59" t="s">
+      <c r="K14" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="L14" s="59"/>
-    </row>
-    <row r="15" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="58"/>
+    </row>
+    <row r="15" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="50">
-        <v>0</v>
-      </c>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50">
-        <v>0</v>
-      </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50">
-        <v>0</v>
-      </c>
-      <c r="I15" s="50"/>
+      <c r="D15" s="49">
+        <v>0</v>
+      </c>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49">
+        <v>0</v>
+      </c>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49">
+        <v>0</v>
+      </c>
+      <c r="I15" s="49"/>
       <c r="J15" s="6" t="e">
         <f>L15</f>
         <v>#DIV/0!</v>
@@ -1480,21 +1503,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="48">
-        <v>0</v>
-      </c>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48">
-        <v>0</v>
-      </c>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48">
-        <v>0</v>
-      </c>
-      <c r="I16" s="48"/>
+      <c r="D16" s="47">
+        <v>0</v>
+      </c>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47">
+        <v>0</v>
+      </c>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47">
+        <v>0</v>
+      </c>
+      <c r="I16" s="47"/>
       <c r="J16" s="10" t="e">
         <f t="shared" ref="J16:J34" si="0">L16</f>
         <v>#DIV/0!</v>
@@ -1505,21 +1528,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B17" s="12"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="49">
-        <v>0</v>
-      </c>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49">
-        <v>0</v>
-      </c>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49">
-        <v>0</v>
-      </c>
-      <c r="I17" s="49"/>
+      <c r="D17" s="48">
+        <v>0</v>
+      </c>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48">
+        <v>0</v>
+      </c>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48">
+        <v>0</v>
+      </c>
+      <c r="I17" s="48"/>
       <c r="J17" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1530,21 +1553,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
-      <c r="D18" s="48">
-        <v>0</v>
-      </c>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48">
-        <v>0</v>
-      </c>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48">
-        <v>0</v>
-      </c>
-      <c r="I18" s="48"/>
+      <c r="D18" s="47">
+        <v>0</v>
+      </c>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47">
+        <v>0</v>
+      </c>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47">
+        <v>0</v>
+      </c>
+      <c r="I18" s="47"/>
       <c r="J18" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1555,21 +1578,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="49">
-        <v>0</v>
-      </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49">
-        <v>0</v>
-      </c>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49">
-        <v>0</v>
-      </c>
-      <c r="I19" s="49"/>
+      <c r="D19" s="48">
+        <v>0</v>
+      </c>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48">
+        <v>0</v>
+      </c>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48">
+        <v>0</v>
+      </c>
+      <c r="I19" s="48"/>
       <c r="J19" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1580,21 +1603,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B20" s="8"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="48">
-        <v>0</v>
-      </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48">
-        <v>0</v>
-      </c>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48">
-        <v>0</v>
-      </c>
-      <c r="I20" s="48"/>
+      <c r="D20" s="47">
+        <v>0</v>
+      </c>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47">
+        <v>0</v>
+      </c>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47">
+        <v>0</v>
+      </c>
+      <c r="I20" s="47"/>
       <c r="J20" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1605,21 +1628,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B21" s="12"/>
       <c r="C21" s="13"/>
-      <c r="D21" s="49">
-        <v>0</v>
-      </c>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49">
-        <v>0</v>
-      </c>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49">
-        <v>0</v>
-      </c>
-      <c r="I21" s="49"/>
+      <c r="D21" s="48">
+        <v>0</v>
+      </c>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48">
+        <v>0</v>
+      </c>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48">
+        <v>0</v>
+      </c>
+      <c r="I21" s="48"/>
       <c r="J21" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1630,21 +1653,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
-      <c r="D22" s="48">
-        <v>0</v>
-      </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48">
-        <v>0</v>
-      </c>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48">
-        <v>0</v>
-      </c>
-      <c r="I22" s="48"/>
+      <c r="D22" s="47">
+        <v>0</v>
+      </c>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47">
+        <v>0</v>
+      </c>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47">
+        <v>0</v>
+      </c>
+      <c r="I22" s="47"/>
       <c r="J22" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1655,21 +1678,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B23" s="12"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="49">
-        <v>0</v>
-      </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49">
-        <v>0</v>
-      </c>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49">
-        <v>0</v>
-      </c>
-      <c r="I23" s="49"/>
+      <c r="D23" s="48">
+        <v>0</v>
+      </c>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48">
+        <v>0</v>
+      </c>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48">
+        <v>0</v>
+      </c>
+      <c r="I23" s="48"/>
       <c r="J23" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1680,21 +1703,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="48">
-        <v>0</v>
-      </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48">
-        <v>0</v>
-      </c>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48">
-        <v>0</v>
-      </c>
-      <c r="I24" s="48"/>
+      <c r="D24" s="47">
+        <v>0</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47">
+        <v>0</v>
+      </c>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47">
+        <v>0</v>
+      </c>
+      <c r="I24" s="47"/>
       <c r="J24" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1705,21 +1728,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B25" s="12"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="49">
-        <v>0</v>
-      </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49">
-        <v>0</v>
-      </c>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49">
-        <v>0</v>
-      </c>
-      <c r="I25" s="49"/>
+      <c r="D25" s="48">
+        <v>0</v>
+      </c>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48">
+        <v>0</v>
+      </c>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48">
+        <v>0</v>
+      </c>
+      <c r="I25" s="48"/>
       <c r="J25" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1730,21 +1753,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="48">
-        <v>0</v>
-      </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48">
-        <v>0</v>
-      </c>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48">
-        <v>0</v>
-      </c>
-      <c r="I26" s="48"/>
+      <c r="D26" s="47">
+        <v>0</v>
+      </c>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47">
+        <v>0</v>
+      </c>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47">
+        <v>0</v>
+      </c>
+      <c r="I26" s="47"/>
       <c r="J26" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1755,21 +1778,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B27" s="12"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="49">
-        <v>0</v>
-      </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49">
-        <v>0</v>
-      </c>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49">
-        <v>0</v>
-      </c>
-      <c r="I27" s="49"/>
+      <c r="D27" s="48">
+        <v>0</v>
+      </c>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48">
+        <v>0</v>
+      </c>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48">
+        <v>0</v>
+      </c>
+      <c r="I27" s="48"/>
       <c r="J27" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1780,21 +1803,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="48">
-        <v>0</v>
-      </c>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48">
-        <v>0</v>
-      </c>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48">
-        <v>0</v>
-      </c>
-      <c r="I28" s="48"/>
+      <c r="D28" s="47">
+        <v>0</v>
+      </c>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47">
+        <v>0</v>
+      </c>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47">
+        <v>0</v>
+      </c>
+      <c r="I28" s="47"/>
       <c r="J28" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1805,21 +1828,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B29" s="12"/>
       <c r="C29" s="13"/>
-      <c r="D29" s="49">
-        <v>0</v>
-      </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49">
-        <v>0</v>
-      </c>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49">
-        <v>0</v>
-      </c>
-      <c r="I29" s="49"/>
+      <c r="D29" s="48">
+        <v>0</v>
+      </c>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48">
+        <v>0</v>
+      </c>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48">
+        <v>0</v>
+      </c>
+      <c r="I29" s="48"/>
       <c r="J29" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1830,21 +1853,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B30" s="8"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="48">
-        <v>0</v>
-      </c>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48">
-        <v>0</v>
-      </c>
-      <c r="G30" s="48"/>
-      <c r="H30" s="48">
-        <v>0</v>
-      </c>
-      <c r="I30" s="48"/>
+      <c r="D30" s="47">
+        <v>0</v>
+      </c>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47">
+        <v>0</v>
+      </c>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47">
+        <v>0</v>
+      </c>
+      <c r="I30" s="47"/>
       <c r="J30" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1855,21 +1878,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
-      <c r="D31" s="49">
-        <v>0</v>
-      </c>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49">
-        <v>0</v>
-      </c>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49">
-        <v>0</v>
-      </c>
-      <c r="I31" s="49"/>
+      <c r="D31" s="48">
+        <v>0</v>
+      </c>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48">
+        <v>0</v>
+      </c>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48">
+        <v>0</v>
+      </c>
+      <c r="I31" s="48"/>
       <c r="J31" s="14" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1880,21 +1903,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B32" s="8"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="48">
-        <v>0</v>
-      </c>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48">
-        <v>0</v>
-      </c>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48">
-        <v>0</v>
-      </c>
-      <c r="I32" s="48"/>
+      <c r="D32" s="47">
+        <v>0</v>
+      </c>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47">
+        <v>0</v>
+      </c>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47">
+        <v>0</v>
+      </c>
+      <c r="I32" s="47"/>
       <c r="J32" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1905,21 +1928,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B33" s="12"/>
       <c r="C33" s="13"/>
-      <c r="D33" s="49">
-        <v>0</v>
-      </c>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49">
-        <v>0</v>
-      </c>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49">
-        <v>0</v>
-      </c>
-      <c r="I33" s="49"/>
+      <c r="D33" s="48">
+        <v>0</v>
+      </c>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48">
+        <v>0</v>
+      </c>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48">
+        <v>0</v>
+      </c>
+      <c r="I33" s="48"/>
       <c r="J33" s="14" t="e">
         <f t="shared" ref="J33" si="2">L33</f>
         <v>#DIV/0!</v>
@@ -1930,21 +1953,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B34" s="8"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="48">
-        <v>0</v>
-      </c>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48">
-        <v>0</v>
-      </c>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48">
-        <v>0</v>
-      </c>
-      <c r="I34" s="48"/>
+      <c r="D34" s="47">
+        <v>0</v>
+      </c>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47">
+        <v>0</v>
+      </c>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47">
+        <v>0</v>
+      </c>
+      <c r="I34" s="47"/>
       <c r="J34" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -1955,26 +1978,26 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="2:12" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="17"/>
-      <c r="D35" s="47">
+      <c r="D35" s="68">
         <f>SUM(D15:E34)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47">
+      <c r="E35" s="68"/>
+      <c r="F35" s="68">
         <f>SUM(F15:G34)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47">
+      <c r="G35" s="68"/>
+      <c r="H35" s="68">
         <f>SUM(H15:I34)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="47"/>
+      <c r="I35" s="68"/>
       <c r="J35" s="18" t="e">
         <f t="shared" ref="J35" si="4">L35</f>
         <v>#DIV/0!</v>
@@ -1987,64 +2010,6 @@
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="H35:I35"/>
@@ -2061,6 +2026,64 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
   </mergeCells>
   <conditionalFormatting sqref="D7">
     <cfRule type="iconSet" priority="8">
@@ -2090,89 +2113,6 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="16" id="{B79D8311-1CFC-4300-85C6-7850B92DBDD0}">
-            <x14:iconSet iconSet="3Arrows">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>SUM('Sales Data'!$H$19:$H$30)</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula" gte="0">
-                <xm:f>SUM('Sales Data'!$H$19:$H$30)</xm:f>
-              </x14:cfvo>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>J7:L7 J8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{44E6DDC4-EEC6-47F2-836B-C0E5F890EB60}">
-            <x14:iconSet iconSet="3Arrows">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>SUM('Sales Data'!$G$19:$G$30)</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula" gte="0">
-                <xm:f>SUM('Sales Data'!$G$19:$G$30)</xm:f>
-              </x14:cfvo>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>H7:H8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="18" id="{D25D609B-49D9-4657-9C4C-FC1EE5C28D21}">
-            <x14:iconSet iconSet="3Arrows">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>SUM('Sales Data'!$F$19:$F$30)</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula" gte="0">
-                <xm:f>SUM('Sales Data'!$F$19:$F$30)</xm:f>
-              </x14:cfvo>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>F7:F8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{46AB3E64-B72B-46EF-A12C-5CC3091BD522}">
-            <x14:iconSet iconSet="3Arrows">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>SUM('Sales Data'!$E$19:$E$30)</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="formula" gte="0">
-                <xm:f>SUM('Sales Data'!$E$19:$E$30)</xm:f>
-              </x14:cfvo>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D7:D8</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{2C0FDE2D-F769-45C0-B9E8-BEA104EA2E09}">
-            <x14:iconSet showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>J17:J34</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="20" id="{7DDFAD2A-082E-485D-93BA-8F764AADBA35}">
             <x14:iconSet custom="1">
               <x14:cfvo type="percent">
@@ -2192,23 +2132,39 @@
           <xm:sqref>B7:B8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{8981632B-ACC0-4645-A47C-BB51039B2116}">
-            <x14:iconSet showValue="0" custom="1">
+          <x14:cfRule type="iconSet" priority="1" id="{862E0F21-8931-4492-9CC2-C0EBB6B89188}">
+            <x14:iconSet custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
+              <x14:cfvo type="formula">
+                <xm:f>SUM('Sales Data'!$D$19:$D$30)</xm:f>
               </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
+              <x14:cfvo type="formula" gte="0">
+                <xm:f>SUM('Sales Data'!$D$19:$D$30)</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
               <x14:cfIcon iconSet="3Arrows" iconId="1"/>
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>J15:J16 J35</xm:sqref>
+          <xm:sqref>B11:B12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="19" id="{46AB3E64-B72B-46EF-A12C-5CC3091BD522}">
+            <x14:iconSet iconSet="3Arrows">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>SUM('Sales Data'!$E$19:$E$30)</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula" gte="0">
+                <xm:f>SUM('Sales Data'!$E$19:$E$30)</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D7:D8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="6" id="{608C2F1B-508E-48F8-A5DA-5975459DCB59}">
@@ -2230,6 +2186,22 @@
           <xm:sqref>D11:D12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="18" id="{D25D609B-49D9-4657-9C4C-FC1EE5C28D21}">
+            <x14:iconSet iconSet="3Arrows">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>SUM('Sales Data'!$F$19:$F$30)</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula" gte="0">
+                <xm:f>SUM('Sales Data'!$F$19:$F$30)</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F7:F8</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="5" id="{A6FBB14D-16A1-4F22-A9A6-5FD7F0D52DFC}">
             <x14:iconSet iconSet="3Arrows">
               <x14:cfvo type="percent">
@@ -2244,6 +2216,22 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>F11:F12</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="17" id="{44E6DDC4-EEC6-47F2-836B-C0E5F890EB60}">
+            <x14:iconSet iconSet="3Arrows">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>SUM('Sales Data'!$G$19:$G$30)</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula" gte="0">
+                <xm:f>SUM('Sales Data'!$G$19:$G$30)</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>H7:H8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="3" id="{A7D84285-9AA9-4F63-B41C-44F74365CA89}">
@@ -2278,41 +2266,188 @@
           <xm:sqref>J11:J12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{862E0F21-8931-4492-9CC2-C0EBB6B89188}">
-            <x14:iconSet custom="1">
+          <x14:cfRule type="iconSet" priority="21" id="{8981632B-ACC0-4645-A47C-BB51039B2116}">
+            <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
-              <x14:cfvo type="formula">
-                <xm:f>SUM('Sales Data'!$D$19:$D$30)</xm:f>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
               </x14:cfvo>
-              <x14:cfvo type="formula" gte="0">
-                <xm:f>SUM('Sales Data'!$D$19:$D$30)</xm:f>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfIcon iconSet="3Arrows" iconId="0"/>
               <x14:cfIcon iconSet="3Arrows" iconId="1"/>
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>B11:B12</xm:sqref>
+          <xm:sqref>J15:J16 J35</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="15" id="{2C0FDE2D-F769-45C0-B9E8-BEA104EA2E09}">
+            <x14:iconSet showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>J17:J34</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="16" id="{B79D8311-1CFC-4300-85C6-7850B92DBDD0}">
+            <x14:iconSet iconSet="3Arrows">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula">
+                <xm:f>SUM('Sales Data'!$H$19:$H$30)</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="formula" gte="0">
+                <xm:f>SUM('Sales Data'!$H$19:$H$30)</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>J7:L7 J8</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000000000000}">
-          <x14:colorSeries theme="8"/>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000009000000}">
+          <x14:colorSeries theme="6"/>
           <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.249977111117893"/>
-          <x14:colorFirst theme="4" tint="-0.249977111117893"/>
-          <x14:colorLast theme="4" tint="-0.249977111117893"/>
-          <x14:colorHigh theme="4" tint="-0.249977111117893"/>
-          <x14:colorLow theme="4" tint="-0.249977111117893"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>'Sales Data'!D31:D42</xm:f>
-              <xm:sqref>B8</xm:sqref>
+              <xm:f>'Sales Data'!F31:F42</xm:f>
+              <xm:sqref>F8</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000008000000}">
+          <x14:colorSeries theme="5"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!E31:E42</xm:f>
+              <xm:sqref>D8</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000007000000}">
+          <x14:colorSeries theme="7"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!G31:G42</xm:f>
+              <xm:sqref>H8</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000006000000}">
+          <x14:colorSeries theme="9"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!H31:H42</xm:f>
+              <xm:sqref>J8</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000005000000}">
+          <x14:colorSeries theme="9"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!I31:I42</xm:f>
+              <xm:sqref>B12</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000004000000}">
+          <x14:colorSeries theme="8"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!J31:J42</xm:f>
+              <xm:sqref>D12</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000003000000}">
+          <x14:colorSeries theme="5"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!K31:K42</xm:f>
+              <xm:sqref>F12</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000002000000}">
+          <x14:colorSeries theme="6"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Sales Data'!L31:L42</xm:f>
+              <xm:sqref>H12</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -2332,131 +2467,19 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000002000000}">
-          <x14:colorSeries theme="6"/>
-          <x14:colorNegative rgb="FFD00000"/>
+        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000000000000}">
+          <x14:colorSeries theme="8"/>
+          <x14:colorNegative theme="5"/>
           <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
+          <x14:colorMarkers theme="4" tint="-0.249977111117893"/>
+          <x14:colorFirst theme="4" tint="-0.249977111117893"/>
+          <x14:colorLast theme="4" tint="-0.249977111117893"/>
+          <x14:colorHigh theme="4" tint="-0.249977111117893"/>
+          <x14:colorLow theme="4" tint="-0.249977111117893"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>'Sales Data'!L31:L42</xm:f>
-              <xm:sqref>H12</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000003000000}">
-          <x14:colorSeries theme="5"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!K31:K42</xm:f>
-              <xm:sqref>F12</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000004000000}">
-          <x14:colorSeries theme="8"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!J31:J42</xm:f>
-              <xm:sqref>D12</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000005000000}">
-          <x14:colorSeries theme="9"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!I31:I42</xm:f>
-              <xm:sqref>B12</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000006000000}">
-          <x14:colorSeries theme="9"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!H31:H42</xm:f>
-              <xm:sqref>J8</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000007000000}">
-          <x14:colorSeries theme="7"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!G31:G42</xm:f>
-              <xm:sqref>H8</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000008000000}">
-          <x14:colorSeries theme="5"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!E31:E42</xm:f>
-              <xm:sqref>D8</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup lineWeight="1.5" displayEmptyCellsAs="gap" xr2:uid="{00000000-0003-0000-0000-000009000000}">
-          <x14:colorSeries theme="6"/>
-          <x14:colorNegative theme="5"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
-          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
-          <x14:colorLast theme="4" tint="0.39997558519241921"/>
-          <x14:colorHigh theme="4"/>
-          <x14:colorLow theme="4"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Sales Data'!F31:F42</xm:f>
-              <xm:sqref>F8</xm:sqref>
+              <xm:f>'Sales Data'!D31:D42</xm:f>
+              <xm:sqref>B8</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -2472,15 +2495,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:N42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="14" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="14" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:14" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" ht="17.25" customHeight="1"/>
+    <row r="3" spans="2:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2493,20 +2516,20 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="45" t="str">
-        <f ca="1">CONCATENATE("SALES ANALYSIS ", YEAR(TODAY())-1)</f>
-        <v>SALES ANALYSIS 2019</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N3" s="45" t="str" cm="1">
+        <f t="array" aca="1" ref="N3" ca="1">CONCATENATE("SALES ANALYSIS ", ReportYear)</f>
+        <v>SALES ANALYSIS 2025</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="28.2" customHeight="1">
       <c r="B4" s="33" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="28.15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="28.2" hidden="1" customHeight="1">
       <c r="B5" s="33"/>
     </row>
-    <row r="6" spans="2:14" s="1" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" s="1" customFormat="1" ht="18.899999999999999" customHeight="1">
       <c r="B6" s="35" t="s">
         <v>4</v>
       </c>
@@ -2527,13 +2550,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="39">
-        <f ca="1">YEAR(TODAY())-3</f>
-        <v>2017</v>
+    <row r="7" spans="2:14" ht="18.899999999999999" customHeight="1">
+      <c r="B7" s="39" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">ReportYear-2</f>
+        <v>2023</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" s="41">
         <v>0</v>
@@ -2570,10 +2593,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B8" s="42"/>
       <c r="C8" s="42" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8" s="43">
         <v>0</v>
@@ -2610,10 +2633,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B9" s="39"/>
       <c r="C9" s="40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="41">
         <v>0</v>
@@ -2650,10 +2673,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B10" s="42"/>
       <c r="C10" s="42" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" s="43">
         <v>0</v>
@@ -2690,10 +2713,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B11" s="39"/>
       <c r="C11" s="40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11" s="41">
         <v>0</v>
@@ -2730,10 +2753,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B12" s="42"/>
       <c r="C12" s="42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12" s="43">
         <v>0</v>
@@ -2770,10 +2793,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B13" s="39"/>
       <c r="C13" s="40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D13" s="41">
         <v>0</v>
@@ -2810,10 +2833,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B14" s="42"/>
       <c r="C14" s="42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D14" s="43">
         <v>0</v>
@@ -2850,10 +2873,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B15" s="39"/>
       <c r="C15" s="40" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D15" s="41">
         <v>0</v>
@@ -2890,10 +2913,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B16" s="42"/>
       <c r="C16" s="42" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D16" s="43">
         <v>0</v>
@@ -2930,10 +2953,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B17" s="39"/>
       <c r="C17" s="40" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D17" s="41">
         <v>0</v>
@@ -2970,10 +2993,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B18" s="42"/>
       <c r="C18" s="42" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D18" s="43">
         <v>0</v>
@@ -3010,13 +3033,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="39">
-        <f ca="1">YEAR(TODAY())-2</f>
-        <v>2018</v>
+    <row r="19" spans="2:14" ht="18.899999999999999" customHeight="1">
+      <c r="B19" s="39" cm="1">
+        <f t="array" aca="1" ref="B19" ca="1">ReportYear-1</f>
+        <v>2024</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="41">
         <v>0</v>
@@ -3053,10 +3076,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B20" s="42"/>
       <c r="C20" s="42" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D20" s="43">
         <v>0</v>
@@ -3093,10 +3116,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B21" s="39"/>
       <c r="C21" s="40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="41">
         <v>0</v>
@@ -3133,10 +3156,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B22" s="42"/>
       <c r="C22" s="42" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D22" s="43">
         <v>0</v>
@@ -3173,10 +3196,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B23" s="39"/>
       <c r="C23" s="40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D23" s="41">
         <v>0</v>
@@ -3213,10 +3236,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B24" s="42"/>
       <c r="C24" s="42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24" s="43">
         <v>0</v>
@@ -3253,10 +3276,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B25" s="39"/>
       <c r="C25" s="40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D25" s="41">
         <v>0</v>
@@ -3293,10 +3316,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B26" s="42"/>
       <c r="C26" s="42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D26" s="43">
         <v>0</v>
@@ -3333,10 +3356,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B27" s="39"/>
       <c r="C27" s="40" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D27" s="41">
         <v>0</v>
@@ -3373,10 +3396,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B28" s="42"/>
       <c r="C28" s="42" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D28" s="43">
         <v>0</v>
@@ -3413,10 +3436,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B29" s="39"/>
       <c r="C29" s="40" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D29" s="41">
         <v>0</v>
@@ -3453,10 +3476,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B30" s="42"/>
       <c r="C30" s="42" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D30" s="43">
         <v>0</v>
@@ -3493,13 +3516,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="39">
-        <f ca="1">YEAR(TODAY())-1</f>
-        <v>2019</v>
+    <row r="31" spans="2:14" ht="18.899999999999999" customHeight="1">
+      <c r="B31" s="39" cm="1">
+        <f t="array" aca="1" ref="B31" ca="1">ReportYear</f>
+        <v>2025</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D31" s="41">
         <v>0</v>
@@ -3536,10 +3559,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B32" s="42"/>
       <c r="C32" s="42" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D32" s="43">
         <v>0</v>
@@ -3576,10 +3599,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B33" s="39"/>
       <c r="C33" s="40" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="41">
         <v>0</v>
@@ -3616,10 +3639,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B34" s="42"/>
       <c r="C34" s="42" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D34" s="43">
         <v>0</v>
@@ -3656,10 +3679,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B35" s="39"/>
       <c r="C35" s="40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D35" s="41">
         <v>0</v>
@@ -3696,10 +3719,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B36" s="42"/>
       <c r="C36" s="42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D36" s="43">
         <v>0</v>
@@ -3736,10 +3759,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B37" s="39"/>
       <c r="C37" s="40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D37" s="41">
         <v>0</v>
@@ -3776,10 +3799,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B38" s="42"/>
       <c r="C38" s="42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D38" s="43">
         <v>0</v>
@@ -3816,10 +3839,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B39" s="39"/>
       <c r="C39" s="40" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D39" s="41">
         <v>0</v>
@@ -3856,10 +3879,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B40" s="42"/>
       <c r="C40" s="42" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D40" s="43">
         <v>0</v>
@@ -3896,10 +3919,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B41" s="39"/>
       <c r="C41" s="40" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D41" s="41">
         <v>0</v>
@@ -3936,10 +3959,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:14" ht="18.899999999999999" customHeight="1">
       <c r="B42" s="37"/>
       <c r="C42" s="37" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D42" s="34">
         <v>0</v>
